--- a/code/ga_pc_builder/ga_results.xlsx
+++ b/code/ga_pc_builder/ga_results.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,148 +413,163 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB6"/>
+  <dimension ref="A1:AE6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>排名</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>總價(NT$)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>相容性懲罰</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>相容性問題</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>CPU_型號</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>CPU_價格</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>CPU_情感分</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>GPU_型號</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>GPU_價格</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>GPU_情感分</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>記憶體_型號</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>記憶體_價格</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>記憶體_情感分</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>主機板_型號</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>主機板_價格</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>主機板_情感分</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>SSD_型號</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>SSD_價格</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>SSD_情感分</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>電源_型號</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>電源_價格</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>電源_情感分</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>機殼_型號</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>機殼_價格</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>機殼_情感分</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>風冷_型號</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>風冷_價格</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>風冷_情感分</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>HDD_型號</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>HDD_價格</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>HDD_情感分</t>
         </is>
       </c>
     </row>
@@ -575,7 +578,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>76549</v>
+        <v>58737</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -583,80 +586,80 @@
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 7 265K【20核】3.9G(↑5.5G) /30M /內顯Xe-core /無風扇</t>
+          <t>Intel Core Ultra 5 245K【14核】4.2G(↑5.2G) /24M /內顯Xe-core /無風扇</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>10200</v>
+        <v>6990</v>
       </c>
       <c r="G2" t="n">
-        <v>0.698</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>微星 RTX5070Ti 16G VENTUS 3X OC(2497MHz/31cm/三風扇/註四年)</t>
+          <t>[搭機優惠] ZOTAC RTX5070 Twin Edge OC(2542MHz/24cm/雙風扇/註五年)</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>31990</v>
+        <v>20990</v>
       </c>
       <c r="J2" t="n">
-        <v>0.612</v>
+        <v>0.479</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>金士頓 32GB(雙通16GB*2) DDR5-6000/CL30 FURY Beast 黑 (獸獵者)~組裝價~</t>
+          <t>UMAX 單條32GB DDR5-4800/CL40</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>12500</v>
+        <v>8888</v>
       </c>
       <c r="M2" t="n">
-        <v>0.635</v>
+        <v>0.533</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>華擎 Z890 Pro-A WiFi(ATX/LAN 2.5Gb+無線/註冊五年保)16+1+1相電源</t>
+          <t>華碩 B860M AYW GAMING WIFI(M-ATX/LAN2.5Gb+無線/註五年/2DIMM)獨家.6+1+</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>5990</v>
+        <v>3990</v>
       </c>
       <c r="P2" t="n">
-        <v>0.65</v>
+        <v>0.572</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>威剛 ADATA LEGEND 900 1TB/Gen4/讀7000/寫4700(單面設計)贈散熱片【五年保】</t>
+          <t>致態 ZhiTai TiPlus7100s 1TB/Gen4/PCIe 4.0/讀7400/寫6900/TLC【五年保】</t>
         </is>
       </c>
       <c r="R2" t="n">
         <v>4999</v>
       </c>
       <c r="S2" t="n">
-        <v>0.728</v>
+        <v>0.5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>振華 LEADEX VII PRO 1000W 黑色 雙8/白金/全模/ATX3.1(PCIe 5.1)/全日系/10年</t>
+          <t>全漢 金鋼彈 750W ATX3.0(PCIe 5.0) 雙8/金牌/全模/主日系/10年保【SFX規格】</t>
         </is>
       </c>
       <c r="U2" t="n">
-        <v>4990</v>
+        <v>3690</v>
       </c>
       <c r="V2" t="n">
-        <v>0.75</v>
+        <v>0.624</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Montech KING 95 PRO 白 顯卡長42/CPU高17.5/六風扇/分艙設計/全景玻璃+網孔/ATX</t>
+          <t>聯力 O11 Dynamic EVO XL 白 顯卡長46/CPU高16.7/雙向翻轉設計/玻璃透側/E-ATX</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>4190</v>
+        <v>7500</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.746</v>
+        <v>0.647</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
@@ -667,15 +670,18 @@
         <v>1690</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.704</v>
-      </c>
+        <v>0.648</v>
+      </c>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>76549</v>
+        <v>59437</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -683,80 +689,80 @@
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 7 265K【20核】3.9G(↑5.5G) /30M /內顯Xe-core /無風扇</t>
+          <t>Intel Core Ultra 5 245K【14核】4.2G(↑5.2G) /24M /內顯Xe-core /無風扇</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>10200</v>
+        <v>6990</v>
       </c>
       <c r="G3" t="n">
-        <v>0.698</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>微星 RTX5070Ti 16G VENTUS 3X OC(2497MHz/31cm/三風扇/註四年)</t>
+          <t>[搭機優惠] ZOTAC RTX5070 Twin Edge OC(2542MHz/24cm/雙風扇/註五年)</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>31990</v>
+        <v>20990</v>
       </c>
       <c r="J3" t="n">
-        <v>0.612</v>
+        <v>0.479</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>金士頓 32GB(雙通16GB*2) DDR5-6000/CL30 FURY Beast 黑 (獸獵者)~組裝價~</t>
+          <t>UMAX 單條32GB DDR5-4800/CL40</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>12500</v>
+        <v>8888</v>
       </c>
       <c r="M3" t="n">
-        <v>0.635</v>
+        <v>0.533</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>華擎 Z890 Pro-A WiFi(ATX/LAN 2.5Gb+無線/註冊五年保)16+1+1相電源</t>
+          <t>技嘉 B860M GAMING WIFI6(M-ATX/LAN2.5G+無線/註五年)8+1+2相</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>5990</v>
+        <v>4690</v>
       </c>
       <c r="P3" t="n">
-        <v>0.65</v>
+        <v>0.572</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>威剛 ADATA LEGEND 900 1TB/Gen4/讀7000/寫4700(單面設計)贈散熱片【五年保】</t>
+          <t>致態 ZhiTai TiPlus7100s 1TB/Gen4/PCIe 4.0/讀7400/寫6900/TLC【五年保】</t>
         </is>
       </c>
       <c r="R3" t="n">
         <v>4999</v>
       </c>
       <c r="S3" t="n">
-        <v>0.728</v>
+        <v>0.5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>振華 LEADEX VII PRO 1000W 黑色 雙8/白金/全模/ATX3.1(PCIe 5.1)/全日系/10年</t>
+          <t>全漢 金鋼彈 750W ATX3.0(PCIe 5.0) 雙8/金牌/全模/主日系/10年保【SFX規格】</t>
         </is>
       </c>
       <c r="U3" t="n">
-        <v>4990</v>
+        <v>3690</v>
       </c>
       <c r="V3" t="n">
-        <v>0.75</v>
+        <v>0.624</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Montech KING 95 PRO 白 顯卡長42/CPU高17.5/六風扇/分艙設計/全景玻璃+網孔/ATX</t>
+          <t>聯力 O11 Dynamic EVO XL 白 顯卡長46/CPU高16.7/雙向翻轉設計/玻璃透側/E-ATX</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>4190</v>
+        <v>7500</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.746</v>
+        <v>0.647</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
@@ -767,15 +773,18 @@
         <v>1690</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.704</v>
-      </c>
+        <v>0.648</v>
+      </c>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>76449</v>
+        <v>55227</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -783,99 +792,102 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 7 265K【20核】3.9G(↑5.5G) /30M /內顯Xe-core /無風扇</t>
+          <t>Intel Core Ultra 5 245K【14核】4.2G(↑5.2G) /24M /內顯Xe-core /無風扇</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>10200</v>
+        <v>6990</v>
       </c>
       <c r="G4" t="n">
-        <v>0.698</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>微星 RTX5070Ti 16G VENTUS 3X OC(2497MHz/31cm/三風扇/註四年)</t>
+          <t>[搭機優惠] ZOTAC RTX5070 Twin Edge OC(2542MHz/24cm/雙風扇/註五年)</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>31990</v>
+        <v>20990</v>
       </c>
       <c r="J4" t="n">
-        <v>0.612</v>
+        <v>0.479</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>金士頓 32GB(雙通16GB*2) DDR5-6000/CL30 FURY Beast 黑 (獸獵者)~組裝價~</t>
+          <t>UMAX 單條32GB DDR5-4800/CL40</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>12500</v>
+        <v>8888</v>
       </c>
       <c r="M4" t="n">
-        <v>0.635</v>
+        <v>0.533</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>華擎 Z890 Pro-A WiFi(ATX/LAN 2.5Gb+無線/註冊五年保)16+1+1相電源</t>
+          <t>華擎 B860M-X WiFi(M-ATX/LAN2.5G+無線/註五年/2DIMM)7+1+1+1+1 相供電</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>5990</v>
+        <v>4990</v>
       </c>
       <c r="P4" t="n">
-        <v>0.65</v>
+        <v>0.572</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>威剛 ADATA LEGEND 900 1TB/Gen4/讀7000/寫4700(單面設計)贈散熱片【五年保】</t>
+          <t>致態 ZhiTai TiPlus7100s 1TB/Gen4/PCIe 4.0/讀7400/寫6900/TLC【五年保】</t>
         </is>
       </c>
       <c r="R4" t="n">
         <v>4999</v>
       </c>
       <c r="S4" t="n">
-        <v>0.728</v>
+        <v>0.5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>振華 LEADEX VII PRO 1000W 黑色 雙8/白金/全模/ATX3.1(PCIe 5.1)/全日系/10年</t>
+          <t>全漢 VITA GM 650W(MIT) 白色版 雙8/金牌/全模/ATX3.1/主日系/10年保</t>
         </is>
       </c>
       <c r="U4" t="n">
-        <v>4990</v>
+        <v>3090</v>
       </c>
       <c r="V4" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Montech KING 95 PRO 白 顯卡長42/CPU高17.5/六風扇/分艙設計/全景玻璃+網孔/ATX</t>
+          <t>華碩 Prime AP201 TG 黑 顯卡長33.8/CPU高17/玻璃透側/前置Type-C/M-ATX</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>4190</v>
+        <v>1890</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.746</v>
+        <v>0.5</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>Scythe 無限6 雪彩版 /6導管/單塔雙扇/高15.4cm/白化版/A.RGB扇/偏移不干涉【WXZ】</t>
+          <t>九州風神 ASSASSIN IV 阿薩辛4 白/7導管/雙塔反葉扇/高16.4cm/不干涉/6年【WXZ】</t>
         </is>
       </c>
       <c r="AA4" t="n">
-        <v>1590</v>
+        <v>3390</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.63</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>88834</v>
+        <v>59217</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -883,90 +895,101 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 7 265K【20核】3.9G(↑5.5G) /30M /內顯Xe-core /無風扇</t>
+          <t>Intel Core Ultra 5 245K【14核】4.2G(↑5.2G) /24M /內顯Xe-core /無風扇</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>10200</v>
+        <v>6990</v>
       </c>
       <c r="G5" t="n">
-        <v>0.698</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>華碩 PRIME-RTX5080-16G(2640MHz/31cm/三風扇/註五年)2.5 Slot</t>
+          <t>[搭機優惠] ZOTAC RTX5070 Twin Edge OC(2542MHz/24cm/雙風扇/註五年)</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>44990</v>
+        <v>20990</v>
       </c>
       <c r="J5" t="n">
-        <v>0.589</v>
+        <v>0.479</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>金士頓 32GB(雙通16GB*2) DDR5-6000/CL30 FURY Beast 黑 (獸獵者)~組裝價~</t>
+          <t>UMAX 單條32GB DDR5-4800/CL40</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>12500</v>
+        <v>8888</v>
       </c>
       <c r="M5" t="n">
-        <v>0.635</v>
+        <v>0.533</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>華擎 Z890 Pro-A WiFi(ATX/LAN 2.5Gb+無線/註冊五年保)16+1+1相電源</t>
+          <t>華碩 B860M AYW GAMING WIFI(M-ATX/LAN2.5Gb+無線/註五年/2DIMM)獨家.6+1+</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>5990</v>
+        <v>3990</v>
       </c>
       <c r="P5" t="n">
-        <v>0.65</v>
+        <v>0.572</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>威剛 ADATA LEGEND 900 1TB/Gen4/讀7000/寫4700(單面設計)贈散熱片【五年保】</t>
+          <t>致態 ZhiTai TiPlus7100s 1TB/Gen4/PCIe 4.0/讀7400/寫6900/TLC【五年保】</t>
         </is>
       </c>
       <c r="R5" t="n">
         <v>4999</v>
       </c>
       <c r="S5" t="n">
-        <v>0.728</v>
+        <v>0.5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>振華 LEADEX VII PRO 1000W 黑色 雙8/白金/全模/ATX3.1(PCIe 5.1)/全日系/10年</t>
+          <t>海韻 FOCUS GX-750 ATX3(750W) 白色版 雙8/金牌/全模組/ATX3.1(PCIe 5.1)10年</t>
         </is>
       </c>
       <c r="U5" t="n">
-        <v>4990</v>
+        <v>4090</v>
       </c>
       <c r="V5" t="n">
-        <v>0.75</v>
+        <v>0.537</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>華碩 Prime AP201 黑 顯卡長33.8/CPU高17/方形進氣孔/前置Type-C/M-ATX</t>
+          <t>Fractal Design Define 7 Compact 黑(靜音) 顯卡長34/CPU高16.9/ATX(DEF</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>1890</v>
+        <v>3790</v>
       </c>
       <c r="Y5" t="n">
         <v>0.5</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>貓頭鷹 NH-D15S /6導管/NF-A15 PWM風扇/雙塔/非對稱式/六年保/高16【WXZ】</t>
+          <t>Scythe 無限6 TUF 黑/6導管/單塔雙扇/高15.4cm/全黑化/A.RGB扇/偏移不干涉【WXZ】</t>
         </is>
       </c>
       <c r="AA5" t="n">
-        <v>3275</v>
+        <v>1690</v>
       </c>
       <c r="AB5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Toshiba 2TB【P300系列】(256M/7200轉/3年保) (HDWD320UZSVA)【限組裝】</t>
+        </is>
+      </c>
+      <c r="AD5" t="n">
+        <v>3790</v>
+      </c>
+      <c r="AE5" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -975,7 +998,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>66008</v>
+        <v>59712</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -983,92 +1006,95 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 7 265K【20核】3.9G(↑5.5G) /30M /內顯Xe-core /無風扇</t>
+          <t>Intel Core Ultra 5 245K【14核】4.2G(↑5.2G) /24M /內顯Xe-core /無風扇</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>10200</v>
+        <v>6990</v>
       </c>
       <c r="G6" t="n">
-        <v>0.698</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>技嘉 RTX5070 WINDFORCE OC SFF 12G(2542MHz/29cm/三風扇/註冊四年保)</t>
+          <t>[搭機優惠] ZOTAC RTX5070 Twin Edge OC(2542MHz/24cm/雙風扇/註五年)</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>22990</v>
+        <v>20990</v>
       </c>
       <c r="J6" t="n">
-        <v>0.612</v>
+        <v>0.479</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>金士頓 32GB(雙通16GB*2) DDR5-6000/CL30 FURY Beast 黑 (獸獵者)~組裝價~</t>
+          <t>UMAX 單條32GB DDR5-4800/CL40</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>12500</v>
+        <v>8888</v>
       </c>
       <c r="M6" t="n">
-        <v>0.635</v>
+        <v>0.533</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>華擎 Z890 Pro-A WiFi(ATX/LAN 2.5Gb+無線/註冊五年保)16+1+1相電源</t>
+          <t>技嘉 Z890 UD WIFI6E(ATX/LAN2.5Gb+無線/註冊四年)14+1+2相</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>5990</v>
+        <v>6990</v>
       </c>
       <c r="P6" t="n">
-        <v>0.65</v>
+        <v>0.46</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>威剛 ADATA LEGEND 900 1TB/Gen4/讀7000/寫4700(單面設計)贈散熱片【五年保】</t>
+          <t>美光 Micron Crucial T500 1TB/Gen4 PCIe 4.0/讀7300/:6800/3D TLC【</t>
         </is>
       </c>
       <c r="R6" t="n">
-        <v>4999</v>
+        <v>7199</v>
       </c>
       <c r="S6" t="n">
-        <v>0.728</v>
+        <v>0.5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>振華 LEADEX VII PRO 850W 黑色 雙8/白金/全模/ATX3.1(PCIe 5.1)/全日系/10年保</t>
+          <t>全漢 VITA GM 750W(MIT) 白色版 雙8/金牌/全模/ATX3.1(PCIe 5.1)/主日系/10年保</t>
         </is>
       </c>
       <c r="U6" t="n">
-        <v>4390</v>
+        <v>3490</v>
       </c>
       <c r="V6" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Montech KING 95 PRO 白 顯卡長42/CPU高17.5/六風扇/分艙設計/全景玻璃+網孔/ATX</t>
+          <t>華碩 Prime AP201 TG 黑 顯卡長33.8/CPU高17/玻璃透側/前置Type-C/M-ATX</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>4190</v>
+        <v>1890</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.746</v>
+        <v>0.5</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>酷碼 Hyper 212 3DHP Black 散熱器/全黑化/高15.8/獨家3D熱管技術【WXZ】</t>
+          <t>貓頭鷹 NH-D15S /6導管/NF-A15 PWM風扇/雙塔/非對稱式/六年保/高16【WXZ】</t>
         </is>
       </c>
       <c r="AA6" t="n">
-        <v>749</v>
+        <v>3275</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.296</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
